--- a/data/trans_dic/IP18A05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,53</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,7</t>
+          <t>0,0; 27,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,59</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,78</t>
+          <t>0,0; 10,84</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,32 +857,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 11,1</t>
+          <t>2,09; 10,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,42</t>
+          <t>0,0; 22,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -891,34 +892,34 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,82</t>
+          <t>0,0; 34,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,63</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,65; 8,67</t>
+          <t>2,81; 8,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 18,64</t>
+          <t>1,35; 19,69</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,72</t>
+          <t>0,0; 6,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,7</t>
+          <t>0,0; 23,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 7,9</t>
+          <t>0,92; 8,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,48</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,01</t>
+          <t>0,49; 4,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,68</t>
+          <t>0,0; 11,83</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,86</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,22</t>
+          <t>0,0; 14,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,19</t>
+          <t>0,0; 45,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,42</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,65</t>
+          <t>0,0; 33,23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,58</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 12,06</t>
+          <t>1,25; 12,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,23</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,17</t>
+          <t>1,35; 8,4</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,44</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,71</t>
+          <t>0,55; 6,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,91</t>
+          <t>0,0; 15,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,38</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 8,77</t>
+          <t>0,98; 8,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 27,82</t>
+          <t>2,22; 29,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,21</t>
+          <t>0,23; 2,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,56</t>
+          <t>1,44; 5,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 18,18</t>
+          <t>2,28; 17,46</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,76</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,55</t>
+          <t>0,51; 4,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,97</t>
+          <t>0,0; 21,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,17</t>
+          <t>0,63; 3,24</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,25</t>
+          <t>0,22; 2,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,41</t>
+          <t>0,0; 12,8</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,45</t>
+          <t>0,22; 1,35</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,63</t>
+          <t>0,33; 1,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,18</t>
+          <t>0,59; 2,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,0</t>
+          <t>0,79; 6,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,4</t>
+          <t>0,22; 1,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,87</t>
+          <t>0,6; 1,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,46</t>
+          <t>0,83; 2,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,85</t>
+          <t>1,7; 9,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,08</t>
+          <t>0,3; 1,08</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,51</t>
+          <t>0,63; 1,47</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,89</t>
+          <t>0,87; 1,94</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,5</t>
+          <t>1,89; 6,48</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3630</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3292</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3642</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2834</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4297</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>8849</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1870</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2662</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1826; 9241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3003</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1635; 9420</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5679</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3318</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5057; 15236</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>404; 5899</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2772</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4090</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3257</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>656; 6191</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3514</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>686; 6385</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3128</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3593</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3997</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3194</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3425</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3894</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4634</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2899</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>573</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4677</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2456</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5597</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3098</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2955</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4449</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4974</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>737; 7176</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>1536; 9549</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1384</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2561</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4287</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2982</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2058</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>6848</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>3770</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4050</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4789</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>611; 6931</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3556</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3358</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1101; 9434</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>615; 8189</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3564</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>649; 5594</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3231; 13138</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1138; 8734</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2563</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3954</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4895</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4530</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>678; 6027</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4719</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4365</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1590; 8247</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>672; 6905</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4085</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5612</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>7422</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>5716</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>7228</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>13489</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>16946</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>8612</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>1320; 8076</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2190; 10369</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3753; 12783</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>797; 6287</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1380; 8572</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4266; 14013</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>5530; 16171</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2233; 12147</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>3656; 13131</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>8696; 20149</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>11414; 25473</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>4383; 15019</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Provincia-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 7,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,23</t>
+          <t>0,0; 25,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>0,0; 11,27</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 3,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 10,6</t>
+          <t>2,12; 10,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,04</t>
+          <t>0,0; 20,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,12</t>
+          <t>2,09; 10,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,78</t>
+          <t>0,0; 31,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,72</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 8,45</t>
+          <t>2,31; 7,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 19,69</t>
+          <t>1,34; 17,82</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,07</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,34</t>
+          <t>0,0; 22,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 8,69</t>
+          <t>0,91; 7,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,6</t>
+          <t>0,54; 4,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,69</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,83</t>
+          <t>0,0; 10,64</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 8,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 3,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,54</t>
+          <t>0,0; 15,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,84</t>
+          <t>0,0; 45,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,8</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,23</t>
+          <t>0,0; 31,62</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 9,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,15</t>
+          <t>1,26; 12,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,4</t>
+          <t>1,31; 8,18</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,21</t>
+          <t>0,58; 5,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,95</t>
+          <t>0,0; 17,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,22 +1582,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,39</t>
+          <t>1,35; 8,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 29,54</t>
+          <t>2,3; 30,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,87</t>
+          <t>1,32; 5,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 17,46</t>
+          <t>1,81; 21,32</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,06</t>
+          <t>0,0; 3,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,98</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,51</t>
+          <t>0,52; 4,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,89</t>
+          <t>0,0; 18,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,24</t>
+          <t>0,55; 3,22</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,22</t>
+          <t>0,21; 2,04</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,8</t>
+          <t>0,0; 11,07</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,35</t>
+          <t>0,22; 1,4</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,56</t>
+          <t>0,41; 1,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,0</t>
+          <t>0,58; 2,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,27</t>
+          <t>1,15; 6,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,37</t>
+          <t>0,19; 1,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,98</t>
+          <t>0,58; 1,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,41</t>
+          <t>0,75; 2,39</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 9,23</t>
+          <t>1,81; 9,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,08</t>
+          <t>0,31; 1,09</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,47</t>
+          <t>0,62; 1,52</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,94</t>
+          <t>0,84; 1,91</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,48</t>
+          <t>1,85; 6,4</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3630</t>
+          <t>0; 3659</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3292</t>
+          <t>0; 3065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3642</t>
+          <t>0; 3657</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2834</t>
+          <t>0; 2947</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2662</t>
+          <t>0; 3330</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1826; 9241</t>
+          <t>1844; 9020</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3003</t>
+          <t>0; 2794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1635; 9420</t>
+          <t>1949; 9618</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5679</t>
+          <t>0; 5148</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3318</t>
+          <t>0; 3276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5057; 15236</t>
+          <t>4167; 14332</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>404; 5899</t>
+          <t>402; 5338</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4090</t>
+          <t>0; 3416</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3257</t>
+          <t>0; 3200</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,12 +2650,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>656; 6191</t>
+          <t>646; 5613</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3514</t>
+          <t>0; 3866</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>686; 6385</t>
+          <t>746; 6618</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3128</t>
+          <t>0; 3449</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3593</t>
+          <t>0; 3233</t>
         </is>
       </c>
     </row>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3997</t>
+          <t>0; 5543</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3194</t>
+          <t>0; 2835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3425</t>
+          <t>0; 3945</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3894</t>
+          <t>0; 4335</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4634</t>
+          <t>0; 4157</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2899</t>
+          <t>0; 2791</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4677</t>
+          <t>0; 4974</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2456</t>
+          <t>0; 2414</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5597</t>
+          <t>0; 5360</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3098</t>
+          <t>0; 2948</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>0; 5149</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>737; 7176</t>
+          <t>742; 7105</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1536; 9549</t>
+          <t>1494; 9290</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4050</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4789</t>
+          <t>0; 4610</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>611; 6931</t>
+          <t>646; 6190</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3556</t>
+          <t>0; 3923</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3358</t>
+          <t>0; 3721</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1101; 9434</t>
+          <t>1517; 9867</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>615; 8189</t>
+          <t>637; 8381</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 3564</t>
+          <t>0; 4091</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>649; 5594</t>
+          <t>648; 5613</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3231; 13138</t>
+          <t>2964; 12561</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1138; 8734</t>
+          <t>906; 10663</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4895</t>
+          <t>0; 4597</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4530</t>
+          <t>0; 4824</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>678; 6027</t>
+          <t>693; 6006</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4719</t>
+          <t>0; 4608</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4365</t>
+          <t>0; 3600</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1590; 8247</t>
+          <t>1386; 8182</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>672; 6905</t>
+          <t>653; 6341</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 4085</t>
+          <t>0; 3533</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1320; 8076</t>
+          <t>1329; 8387</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2190; 10369</t>
+          <t>2710; 10542</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3753; 12783</t>
+          <t>3692; 13046</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>797; 6287</t>
+          <t>1150; 6645</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1380; 8572</t>
+          <t>1172; 8518</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4266; 14013</t>
+          <t>4112; 14009</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5530; 16171</t>
+          <t>5013; 16009</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2233; 12147</t>
+          <t>2388; 12110</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656; 13131</t>
+          <t>3832; 13324</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8696; 20149</t>
+          <t>8545; 20865</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11414; 25473</t>
+          <t>10957; 25045</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4383; 15019</t>
+          <t>4295; 14847</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A05-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Provincia-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,29 +649,29 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,45%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,4%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -732,12 +732,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 24,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,27</t>
+          <t>0,0; 10,7</t>
         </is>
       </c>
     </row>
@@ -794,37 +794,37 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9,11%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,93%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,05%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 10,35</t>
+          <t>1,76; 10,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,5</t>
+          <t>0,0; 37,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 10,34</t>
+          <t>2,11; 11,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,52</t>
+          <t>0,0; 16,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,63</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 7,95</t>
+          <t>2,65; 8,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 17,82</t>
+          <t>1,14; 20,02</t>
         </is>
       </c>
     </row>
@@ -934,37 +934,37 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,45%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,07</t>
+          <t>0,92; 7,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,88</t>
+          <t>0,0; 7,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,77</t>
+          <t>0,54; 5,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,69</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,64</t>
+          <t>0,0; 10,74</t>
         </is>
       </c>
     </row>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1292,12 +1292,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 45,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1312,12 +1312,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,43</t>
+          <t>0,0; 8,42</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,62</t>
+          <t>0,0; 29,58</t>
         </is>
       </c>
     </row>
@@ -1354,27 +1354,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>5,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>2,74%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,44</t>
+          <t>1,27; 12,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 12,03</t>
+          <t>0,0; 9,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,18</t>
+          <t>1,87; 8,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,3%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,81%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,38</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1,27; 8,77</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1,93; 28,93</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,25</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,43</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,58; 5,55</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 17,6</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,78</t>
+          <t>0,68; 5,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 30,23</t>
+          <t>0,0; 23,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,02</t>
+          <t>0,23; 2,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,61</t>
+          <t>1,58; 5,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 21,32</t>
+          <t>1,91; 20,34</t>
         </is>
       </c>
     </row>
@@ -1629,34 +1629,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,81</t>
+          <t>0,52; 4,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1712,17 +1712,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 15,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,5</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1732,17 +1732,17 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,22</t>
+          <t>0,56; 3,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,04</t>
+          <t>0,25; 2,25</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,07</t>
+          <t>0,0; 10,53</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4,53%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>0,62%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0,85%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,89%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -1842,57 +1842,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,59</t>
+          <t>0,58; 1,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,04</t>
+          <t>0,76; 2,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,62</t>
+          <t>2,0; 10,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,37</t>
+          <t>0,24; 1,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,98</t>
+          <t>0,4; 1,63</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,39</t>
+          <t>0,65; 2,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,2</t>
+          <t>1,0; 7,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,09</t>
+          <t>0,31; 1,08</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,52</t>
+          <t>0,61; 1,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,91</t>
+          <t>0,83; 1,89</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,4</t>
+          <t>2,07; 6,8</t>
         </is>
       </c>
     </row>
@@ -1951,13 +1951,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,29 +2141,29 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>730</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>577</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>577</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3659</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3065</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3279</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2715</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3657</t>
+          <t>0; 3832</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2947</t>
+          <t>0; 2492</t>
         </is>
       </c>
     </row>
@@ -2286,37 +2286,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2354,37 +2354,37 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>4297</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4552</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>359</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1672</t>
         </is>
       </c>
     </row>
@@ -2422,17 +2422,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3330</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1844; 9020</t>
+          <t>1641; 9419</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2794</t>
+          <t>0; 5464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3277</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1949; 9618</t>
+          <t>1841; 9674</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5148</t>
+          <t>0; 2111</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2462,17 +2462,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3276</t>
+          <t>0; 3159</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4167; 14332</t>
+          <t>4773; 15625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>402; 5338</t>
+          <t>315; 5511</t>
         </is>
       </c>
     </row>
@@ -2494,37 +2494,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2562,57 +2562,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>675</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1039</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2772</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>685</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2772</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>948</t>
         </is>
       </c>
     </row>
@@ -2630,17 +2630,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3416</t>
+          <t>655; 5628</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3444</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3200</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>646; 5613</t>
+          <t>0; 5204</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2984</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2670,17 +2670,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>746; 6618</t>
+          <t>745; 6944</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3449</t>
+          <t>0; 2801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3233</t>
+          <t>0; 2965</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,37 +2765,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>873</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5543</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4115</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2835</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4376</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3945</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2872</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4335</t>
+          <t>0; 4901</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4157</t>
+          <t>0; 4102</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2791</t>
+          <t>0; 2828</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -2988,34 +2988,34 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>961</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>559</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5538</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2417</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2414</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5360</t>
+          <t>0; 5351</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2948</t>
+          <t>0; 2841</t>
         </is>
       </c>
     </row>
@@ -3118,27 +3118,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -3186,27 +3186,27 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>2955</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>1494</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2955</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5149</t>
+          <t>753; 7122</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>742; 7105</t>
+          <t>0; 5223</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1494; 9290</t>
+          <t>2125; 9285</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4287</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1384</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>2561</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>788</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4287</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>860</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3770</t>
+          <t>3884</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3955</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4610</t>
+          <t>0; 3404</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>646; 6190</t>
+          <t>1424; 9859</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 3923</t>
+          <t>538; 8057</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3958</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3721</t>
+          <t>0; 4619</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1517; 9867</t>
+          <t>758; 6365</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>637; 8381</t>
+          <t>0; 4652</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4091</t>
+          <t>0; 4272</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>648; 5613</t>
+          <t>644; 6144</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2964; 12561</t>
+          <t>3534; 12449</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>906; 10663</t>
+          <t>910; 9701</t>
         </is>
       </c>
     </row>
@@ -3529,29 +3529,29 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,34 +3597,34 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2563</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>1390</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1403</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2563</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>616</t>
         </is>
       </c>
     </row>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 4597</t>
+          <t>689; 6077</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4824</t>
+          <t>0; 3996</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3093</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>693; 6006</t>
+          <t>0; 5262</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 4608</t>
+          <t>0; 4436</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3700,17 +3700,17 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1386; 8182</t>
+          <t>1430; 8054</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>653; 6341</t>
+          <t>788; 7013</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 3533</t>
+          <t>0; 3246</t>
         </is>
       </c>
     </row>
@@ -3742,37 +3742,37 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>9524</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>5513</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>3704</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>5612</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>7422</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>9524</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>5716</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8256</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1329; 8387</t>
+          <t>1386; 8710</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2710; 10542</t>
+          <t>4125; 13234</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3692; 13046</t>
+          <t>5075; 16503</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1150; 6645</t>
+          <t>2435; 12689</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1172; 8518</t>
+          <t>1435; 8668</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4112; 14009</t>
+          <t>2631; 10814</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5013; 16009</t>
+          <t>4139; 13964</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>2388; 12110</t>
+          <t>952; 7018</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3832; 13324</t>
+          <t>3768; 13215</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8545; 20865</t>
+          <t>8313; 20692</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10957; 25045</t>
+          <t>10889; 24821</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4295; 14847</t>
+          <t>4507; 14770</t>
         </is>
       </c>
     </row>
